--- a/dbsyteil3.xlsx
+++ b/dbsyteil3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="88">
   <si>
     <t>Ferienwohnung</t>
   </si>
@@ -233,13 +233,7 @@
     <t>DatumBis</t>
   </si>
   <si>
-    <t>max. 30</t>
-  </si>
-  <si>
     <t>Kunde_Email</t>
-  </si>
-  <si>
-    <t>max. 254</t>
   </si>
   <si>
     <t>Kunde(Email)</t>
@@ -1795,8 +1789,8 @@
       <c r="D48" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>73</v>
+      <c r="E48" s="10">
+        <v>30.0</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>29</v>
@@ -1817,14 +1811,14 @@
     <row r="49">
       <c r="A49" s="6"/>
       <c r="B49" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E49" s="10" t="s">
-        <v>75</v>
+      <c r="E49" s="10">
+        <v>254.0</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>29</v>
@@ -1836,7 +1830,7 @@
         <v>33</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>39</v>
@@ -1845,7 +1839,7 @@
     <row r="50">
       <c r="A50" s="6"/>
       <c r="B50" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="5" t="s">
@@ -1867,7 +1861,7 @@
     <row r="51">
       <c r="A51" s="6"/>
       <c r="B51" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="5" t="s">
@@ -1889,7 +1883,7 @@
     <row r="52">
       <c r="A52" s="6"/>
       <c r="B52" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="5" t="s">
@@ -1911,7 +1905,7 @@
     <row r="53">
       <c r="A53" s="6"/>
       <c r="B53" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="5" t="s">
@@ -1929,13 +1923,13 @@
       </c>
       <c r="I53" s="6"/>
       <c r="J53" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6"/>
       <c r="B54" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="5" t="s">
@@ -1959,7 +1953,7 @@
     <row r="55">
       <c r="A55" s="6"/>
       <c r="B55" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="5" t="s">
@@ -1977,7 +1971,7 @@
       </c>
       <c r="I55" s="6"/>
       <c r="J55" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
@@ -2016,7 +2010,7 @@
         <v>33</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>39</v>
@@ -2025,7 +2019,7 @@
     <row r="58">
       <c r="A58" s="6"/>
       <c r="B58" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="5" t="s">
@@ -2049,7 +2043,7 @@
     <row r="59">
       <c r="A59" s="6"/>
       <c r="B59" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="5" t="s">
@@ -2071,7 +2065,7 @@
     <row r="60">
       <c r="A60" s="6"/>
       <c r="B60" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="5" t="s">
@@ -2089,7 +2083,7 @@
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61">
